--- a/Mod_Korean/Lang/KR/Game/Race.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Race.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">yerles</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.252</t>
+    <t xml:space="preserve">EA 23.260</t>
   </si>
   <si>
     <t xml:space="preserve">イエルス</t>

--- a/Mod_Korean/Lang/KR/Game/Race.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Race.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">yerles</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.260</t>
+    <t xml:space="preserve">EA 23.267</t>
   </si>
   <si>
     <t xml:space="preserve">イエルス</t>

--- a/Mod_Korean/Lang/KR/Game/Race.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Race.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="358">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">yerles</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.267</t>
+    <t xml:space="preserve">EA 23.281</t>
   </si>
   <si>
     <t xml:space="preserve">イエルス</t>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">The Yerles, people of the rising New Kingdom in Sierre Terre, trace their lineage back to slaves who escaped from Eulderna. Harboring deep-seated hatred towards the empire and everything it represents; they have established the pinnacle of mechanical civilizations in Sierre. Gifted with a heightened learning capacity, adept in handling mechanized armaments, they acquire feats faster than any other races.</t>
   </si>
   <si>
-    <t xml:space="preserve">シエラ・テールで急速に台頭してきた新王国イエルの民がイェルスです。彼らの祖先はエウダーナから脱走した奴隷であり、帝国と帝国の生み出した全てのものを憎んでいます。シエラ随一の機械文明を築き上げた彼らは、高い学習能力を持ち、機械武装の扱いにたけ、他の種族よりも早くフィートを獲得できます。</t>
+    <t xml:space="preserve">シエラ・テールで急速に台頭してきた新王国イエルの民がイエルスです。彼らの祖先はエウダーナから脱走した奴隷であり、帝国と帝国の生み出した全てのものを憎んでいます。シエラ随一の機械文明を築き上げた彼らは、高い学習能力を持ち、機械武装の扱いにたけ、他の種族よりも早くフィートを獲得できます。</t>
   </si>
   <si>
     <t xml:space="preserve">eulderna</t>
@@ -336,6 +336,12 @@
   </si>
   <si>
     <t xml:space="preserve">スライム</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slimes are amorphous, gelatinous beings with bodies that lack a fixed shape. They may appear fragile and are often called the weakest of monsters, yet they possess a mysterious potential to absorb whatever they take in and transform it into their own strength. Even if you were to awaken one day as a slime, there would be no need to despair. That humble body is merely the beginning of an endless path of evolution.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">スライムは不定形の体を持つ粘体生物です。見た目は頼りなく、最弱の魔物と呼ばれることもありますが、あらゆるものを取り込み、自らの力へと変えていく不思議な可能性を秘めています。もし目覚めたときに自分がスライムだったとしても、嘆く必要はありません。その体は、無限の進化へと続く始まりなのです。</t>
   </si>
   <si>
     <t xml:space="preserve">wolf</t>
@@ -1188,10 +1194,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>233</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
@@ -1200,7 +1206,7 @@
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G3" t="s">
         <v>11</v>
@@ -1214,10 +1220,10 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C4" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -1226,7 +1232,7 @@
         <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G4" t="s">
         <v>15</v>
@@ -1240,10 +1246,10 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D5" t="s">
         <v>17</v>
@@ -1252,7 +1258,7 @@
         <v>18</v>
       </c>
       <c r="F5" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G5" t="s">
         <v>19</v>
@@ -1266,10 +1272,10 @@
         <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D6" t="s">
         <v>22</v>
@@ -1278,7 +1284,7 @@
         <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="G6" t="s">
         <v>24</v>
@@ -1292,10 +1298,10 @@
         <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D7" t="s">
         <v>26</v>
@@ -1304,7 +1310,7 @@
         <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="G7" t="s">
         <v>28</v>
@@ -1318,10 +1324,10 @@
         <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C8" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D8" t="s">
         <v>30</v>
@@ -1330,7 +1336,7 @@
         <v>31</v>
       </c>
       <c r="F8" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="G8" t="s">
         <v>32</v>
@@ -1344,10 +1350,10 @@
         <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C9" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D9" t="s">
         <v>35</v>
@@ -1356,7 +1362,7 @@
         <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="G9" t="s">
         <v>37</v>
@@ -1370,10 +1376,10 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C10" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D10" t="s">
         <v>39</v>
@@ -1382,7 +1388,7 @@
         <v>40</v>
       </c>
       <c r="F10" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="G10" t="s">
         <v>41</v>
@@ -1396,10 +1402,10 @@
         <v>43</v>
       </c>
       <c r="B11" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C11" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D11" t="s">
         <v>43</v>
@@ -1408,7 +1414,7 @@
         <v>44</v>
       </c>
       <c r="F11" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="G11" t="s">
         <v>45</v>
@@ -1422,10 +1428,10 @@
         <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C12" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D12" t="s">
         <v>47</v>
@@ -1434,7 +1440,7 @@
         <v>48</v>
       </c>
       <c r="F12" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="G12" t="s">
         <v>49</v>
@@ -1448,10 +1454,10 @@
         <v>51</v>
       </c>
       <c r="B13" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C13" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D13" t="s">
         <v>51</v>
@@ -1460,7 +1466,7 @@
         <v>52</v>
       </c>
       <c r="F13" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="G13" t="s">
         <v>53</v>
@@ -1474,10 +1480,10 @@
         <v>55</v>
       </c>
       <c r="B14" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C14" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D14" t="s">
         <v>55</v>
@@ -1486,7 +1492,7 @@
         <v>56</v>
       </c>
       <c r="F14" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="G14" t="s">
         <v>57</v>
@@ -1500,10 +1506,10 @@
         <v>59</v>
       </c>
       <c r="B15" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>59</v>
@@ -1512,7 +1518,7 @@
         <v>60</v>
       </c>
       <c r="F15" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G15" t="s">
         <v>61</v>
@@ -1526,10 +1532,10 @@
         <v>63</v>
       </c>
       <c r="B16" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C16" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D16" t="s">
         <v>63</v>
@@ -1538,7 +1544,7 @@
         <v>64</v>
       </c>
       <c r="F16" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="G16" t="s">
         <v>65</v>
@@ -1552,10 +1558,10 @@
         <v>67</v>
       </c>
       <c r="B17" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C17" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D17" t="s">
         <v>67</v>
@@ -1564,7 +1570,7 @@
         <v>68</v>
       </c>
       <c r="F17" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="G17" t="s">
         <v>69</v>
@@ -1578,10 +1584,10 @@
         <v>71</v>
       </c>
       <c r="B18" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C18" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D18" t="s">
         <v>71</v>
@@ -1590,7 +1596,7 @@
         <v>72</v>
       </c>
       <c r="F18" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G18" t="s">
         <v>73</v>
@@ -1604,10 +1610,10 @@
         <v>75</v>
       </c>
       <c r="B19" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C19" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D19" t="s">
         <v>75</v>
@@ -1616,7 +1622,7 @@
         <v>76</v>
       </c>
       <c r="F19" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="G19" t="s">
         <v>77</v>
@@ -1630,10 +1636,10 @@
         <v>79</v>
       </c>
       <c r="B20" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C20" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D20" t="s">
         <v>79</v>
@@ -1642,7 +1648,7 @@
         <v>80</v>
       </c>
       <c r="F20" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G20" t="s">
         <v>81</v>
@@ -1656,10 +1662,10 @@
         <v>83</v>
       </c>
       <c r="B21" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C21" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D21" t="s">
         <v>84</v>
@@ -1668,7 +1674,7 @@
         <v>85</v>
       </c>
       <c r="F21" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="G21" t="s">
         <v>86</v>
@@ -1682,10 +1688,10 @@
         <v>88</v>
       </c>
       <c r="B22" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C22" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D22" t="s">
         <v>88</v>
@@ -1701,10 +1707,10 @@
         <v>90</v>
       </c>
       <c r="B23" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C23" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D23" t="s">
         <v>91</v>
@@ -1720,10 +1726,10 @@
         <v>93</v>
       </c>
       <c r="B24" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C24" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D24" t="s">
         <v>93</v>
@@ -1739,10 +1745,10 @@
         <v>95</v>
       </c>
       <c r="B25" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C25" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D25" t="s">
         <v>95</v>
@@ -1758,10 +1764,10 @@
         <v>97</v>
       </c>
       <c r="B26" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C26" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D26" t="s">
         <v>97</v>
@@ -1777,10 +1783,10 @@
         <v>99</v>
       </c>
       <c r="B27" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C27" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D27" t="s">
         <v>99</v>
@@ -1796,10 +1802,10 @@
         <v>101</v>
       </c>
       <c r="B28" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C28" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D28" t="s">
         <v>101</v>
@@ -1815,10 +1821,10 @@
         <v>103</v>
       </c>
       <c r="B29" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C29" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D29" t="s">
         <v>103</v>
@@ -1834,10 +1840,10 @@
         <v>105</v>
       </c>
       <c r="B30" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C30" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D30" t="s">
         <v>105</v>
@@ -1845,1183 +1851,1187 @@
       <c r="E30" t="s">
         <v>106</v>
       </c>
-      <c r="G30"/>
-      <c r="H30"/>
+      <c r="G30" t="s">
+        <v>107</v>
+      </c>
+      <c r="H30" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B31" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C31" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D31" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E31" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G31"/>
       <c r="H31"/>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B32" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C32" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D32" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E32" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G32"/>
       <c r="H32"/>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B33" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C33" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D33" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G33"/>
       <c r="H33"/>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B34" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C34" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D34" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E34" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G34"/>
       <c r="H34"/>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B35" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C35" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D35" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E35" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G35"/>
       <c r="H35"/>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B36" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C36" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D36" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E36" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G36"/>
       <c r="H36"/>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B37" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C37" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D37" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E37" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G37"/>
       <c r="H37"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B38" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C38" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D38" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E38" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G38"/>
       <c r="H38"/>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B39" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C39" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D39" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E39" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G39"/>
       <c r="H39"/>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B40" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C40" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D40" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E40" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G40"/>
       <c r="H40"/>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B41" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C41" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D41" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E41" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G41"/>
       <c r="H41"/>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B42" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C42" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D42" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E42" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G42"/>
       <c r="H42"/>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B43" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C43" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D43" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E43" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G43"/>
       <c r="H43"/>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B44" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C44" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D44" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E44" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G44"/>
       <c r="H44"/>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B45" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C45" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D45" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E45" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G45"/>
       <c r="H45"/>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B46" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C46" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D46" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E46" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G46"/>
       <c r="H46"/>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B47" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C47" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D47" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E47" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G47"/>
       <c r="H47"/>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B48" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C48" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D48" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E48" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G48"/>
       <c r="H48"/>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B49" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C49" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D49" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E49" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G49"/>
       <c r="H49"/>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B50" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C50" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D50" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E50" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G50"/>
       <c r="H50"/>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B51" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C51" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D51" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E51" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G51"/>
       <c r="H51"/>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B52" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C52" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D52" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E52" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G52"/>
       <c r="H52"/>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B53" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C53" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D53" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E53" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G53"/>
       <c r="H53"/>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B54" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C54" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D54" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E54" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G54"/>
       <c r="H54"/>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B55" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C55" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D55" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E55" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G55"/>
       <c r="H55"/>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B56" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C56" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D56" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E56" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G56"/>
       <c r="H56"/>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B57" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C57" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D57" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E57" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G57"/>
       <c r="H57"/>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B58" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C58" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D58" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E58" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G58"/>
       <c r="H58"/>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B59" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C59" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D59" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E59" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G59"/>
       <c r="H59"/>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B60" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C60" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D60" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E60" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G60"/>
       <c r="H60"/>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B61" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C61" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D61" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E61" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G61"/>
       <c r="H61"/>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B62" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C62" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D62" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E62" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G62"/>
       <c r="H62"/>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B63" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C63" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D63" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E63" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G63"/>
       <c r="H63"/>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B64" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C64" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D64" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E64" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G64"/>
       <c r="H64"/>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B65" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C65" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D65" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E65" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G65"/>
       <c r="H65"/>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B66" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C66" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D66" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E66" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G66"/>
       <c r="H66"/>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B67" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C67" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D67" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E67" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G67"/>
       <c r="H67"/>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B68" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C68" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D68" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E68" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G68"/>
       <c r="H68"/>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B69" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C69" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D69" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E69" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G69"/>
       <c r="H69"/>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B70" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C70" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D70" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E70" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G70"/>
       <c r="H70"/>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B71" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C71" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D71" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E71" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G71"/>
       <c r="H71"/>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B72" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C72" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D72" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E72" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G72"/>
       <c r="H72"/>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B73" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C73" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D73" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E73" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G73"/>
       <c r="H73"/>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B74" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C74" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D74" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E74" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G74"/>
       <c r="H74"/>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B75" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C75" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D75" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E75" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G75"/>
       <c r="H75"/>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B76" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C76" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D76" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E76" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G76"/>
       <c r="H76"/>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B77" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C77" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D77" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E77" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G77"/>
       <c r="H77"/>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B78" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C78" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D78" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E78" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G78"/>
       <c r="H78"/>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B79" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C79" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D79" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E79" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G79"/>
       <c r="H79"/>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B80" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C80" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D80" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E80" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G80"/>
       <c r="H80"/>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B81" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C81" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D81" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E81" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G81"/>
       <c r="H81"/>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B82" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C82" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D82" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E82" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G82"/>
       <c r="H82"/>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B83" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C83" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D83" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E83" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G83"/>
       <c r="H83"/>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B84" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C84" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D84" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E84" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="G84"/>
       <c r="H84"/>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B85" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C85" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D85" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E85" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G85"/>
       <c r="H85"/>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B86" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C86" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D86" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E86" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="G86"/>
       <c r="H86"/>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B87" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C87" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D87" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E87" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="G87"/>
       <c r="H87"/>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B88" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C88" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D88" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E88" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="G88"/>
       <c r="H88"/>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B89" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C89" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D89" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E89" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="G89"/>
       <c r="H89"/>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B90" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C90" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D90" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E90" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G90"/>
       <c r="H90"/>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B91" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C91" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D91" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E91" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G91"/>
       <c r="H91"/>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B92" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C92" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D92" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E92" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G92"/>
       <c r="H92"/>

--- a/Mod_Korean/Lang/KR/Game/Race.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Race.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">yerles</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.282 Patch 2</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">イエルス</t>

--- a/Mod_Korean/Lang/KR/Game/Race.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Race.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="366">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">yerles</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.287</t>
+    <t xml:space="preserve">EA 23.295</t>
   </si>
   <si>
     <t xml:space="preserve">イエルス</t>
@@ -281,6 +281,18 @@
     <t xml:space="preserve">古代蟹は最も古い蟹の種族で、水辺を好み、生息する地域に適応し様々な属性へと進化しています。基本的には美味しいものの、属性によって風味も変化します。筋力と耐久に秀で、その巨大なハサミで敵を拘束し、また泡のブレスを吐くことができます。</t>
   </si>
   <si>
+    <t xml:space="preserve">ratkin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ラトキン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">werewolf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">人狼</t>
+  </si>
+  <si>
     <t xml:space="preserve">goblin</t>
   </si>
   <si>
@@ -360,6 +372,15 @@
   </si>
   <si>
     <t xml:space="preserve">ウサギ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rabbitkin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ravian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ラビアン</t>
   </si>
   <si>
     <t xml:space="preserve">sheep</t>
@@ -1197,10 +1218,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="C3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
@@ -1209,7 +1230,7 @@
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="G3" t="s">
         <v>11</v>
@@ -1223,10 +1244,10 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C4" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -1235,7 +1256,7 @@
         <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="G4" t="s">
         <v>15</v>
@@ -1249,10 +1270,10 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C5" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="D5" t="s">
         <v>17</v>
@@ -1261,7 +1282,7 @@
         <v>18</v>
       </c>
       <c r="F5" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="G5" t="s">
         <v>19</v>
@@ -1275,10 +1296,10 @@
         <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C6" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="D6" t="s">
         <v>22</v>
@@ -1287,7 +1308,7 @@
         <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="G6" t="s">
         <v>24</v>
@@ -1301,10 +1322,10 @@
         <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C7" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="D7" t="s">
         <v>26</v>
@@ -1313,7 +1334,7 @@
         <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="G7" t="s">
         <v>28</v>
@@ -1327,10 +1348,10 @@
         <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C8" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="D8" t="s">
         <v>30</v>
@@ -1339,7 +1360,7 @@
         <v>31</v>
       </c>
       <c r="F8" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="G8" t="s">
         <v>32</v>
@@ -1353,10 +1374,10 @@
         <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C9" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="D9" t="s">
         <v>35</v>
@@ -1365,7 +1386,7 @@
         <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="G9" t="s">
         <v>37</v>
@@ -1379,10 +1400,10 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C10" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="D10" t="s">
         <v>39</v>
@@ -1391,7 +1412,7 @@
         <v>40</v>
       </c>
       <c r="F10" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="G10" t="s">
         <v>41</v>
@@ -1405,10 +1426,10 @@
         <v>43</v>
       </c>
       <c r="B11" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C11" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="D11" t="s">
         <v>43</v>
@@ -1417,7 +1438,7 @@
         <v>44</v>
       </c>
       <c r="F11" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="G11" t="s">
         <v>45</v>
@@ -1431,10 +1452,10 @@
         <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="C12" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="D12" t="s">
         <v>47</v>
@@ -1443,7 +1464,7 @@
         <v>48</v>
       </c>
       <c r="F12" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="G12" t="s">
         <v>49</v>
@@ -1457,10 +1478,10 @@
         <v>51</v>
       </c>
       <c r="B13" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C13" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D13" t="s">
         <v>51</v>
@@ -1469,7 +1490,7 @@
         <v>52</v>
       </c>
       <c r="F13" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="G13" t="s">
         <v>53</v>
@@ -1483,10 +1504,10 @@
         <v>55</v>
       </c>
       <c r="B14" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C14" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="D14" t="s">
         <v>55</v>
@@ -1495,7 +1516,7 @@
         <v>56</v>
       </c>
       <c r="F14" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="G14" t="s">
         <v>57</v>
@@ -1509,10 +1530,10 @@
         <v>59</v>
       </c>
       <c r="B15" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="C15" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="D15" t="s">
         <v>59</v>
@@ -1521,7 +1542,7 @@
         <v>60</v>
       </c>
       <c r="F15" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="G15" t="s">
         <v>61</v>
@@ -1535,10 +1556,10 @@
         <v>63</v>
       </c>
       <c r="B16" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C16" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="D16" t="s">
         <v>63</v>
@@ -1547,7 +1568,7 @@
         <v>64</v>
       </c>
       <c r="F16" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="G16" t="s">
         <v>65</v>
@@ -1561,10 +1582,10 @@
         <v>67</v>
       </c>
       <c r="B17" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="C17" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="D17" t="s">
         <v>67</v>
@@ -1573,7 +1594,7 @@
         <v>68</v>
       </c>
       <c r="F17" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="G17" t="s">
         <v>69</v>
@@ -1587,10 +1608,10 @@
         <v>71</v>
       </c>
       <c r="B18" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C18" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="D18" t="s">
         <v>71</v>
@@ -1599,7 +1620,7 @@
         <v>72</v>
       </c>
       <c r="F18" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="G18" t="s">
         <v>73</v>
@@ -1613,10 +1634,10 @@
         <v>75</v>
       </c>
       <c r="B19" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="C19" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="D19" t="s">
         <v>75</v>
@@ -1625,7 +1646,7 @@
         <v>76</v>
       </c>
       <c r="F19" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="G19" t="s">
         <v>77</v>
@@ -1639,10 +1660,10 @@
         <v>79</v>
       </c>
       <c r="B20" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="C20" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="D20" t="s">
         <v>79</v>
@@ -1651,7 +1672,7 @@
         <v>80</v>
       </c>
       <c r="F20" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="G20" t="s">
         <v>81</v>
@@ -1665,10 +1686,10 @@
         <v>83</v>
       </c>
       <c r="B21" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C21" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="D21" t="s">
         <v>84</v>
@@ -1677,7 +1698,7 @@
         <v>85</v>
       </c>
       <c r="F21" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="G21" t="s">
         <v>86</v>
@@ -1691,10 +1712,7 @@
         <v>88</v>
       </c>
       <c r="B22" t="s">
-        <v>236</v>
-      </c>
-      <c r="C22" t="s">
-        <v>268</v>
+        <v>9</v>
       </c>
       <c r="D22" t="s">
         <v>88</v>
@@ -1710,48 +1728,45 @@
         <v>90</v>
       </c>
       <c r="B23" t="s">
-        <v>237</v>
-      </c>
-      <c r="C23" t="s">
-        <v>269</v>
+        <v>9</v>
       </c>
       <c r="D23" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23" t="s">
         <v>91</v>
-      </c>
-      <c r="E23" t="s">
-        <v>92</v>
       </c>
       <c r="G23"/>
       <c r="H23"/>
     </row>
     <row r="24">
       <c r="A24" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" t="s">
+        <v>243</v>
+      </c>
+      <c r="C24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D24" t="s">
+        <v>92</v>
+      </c>
+      <c r="E24" t="s">
         <v>93</v>
-      </c>
-      <c r="B24" t="s">
-        <v>237</v>
-      </c>
-      <c r="C24" t="s">
-        <v>270</v>
-      </c>
-      <c r="D24" t="s">
-        <v>93</v>
-      </c>
-      <c r="E24" t="s">
-        <v>94</v>
       </c>
       <c r="G24"/>
       <c r="H24"/>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B25" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C25" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="D25" t="s">
         <v>95</v>
@@ -1767,10 +1782,10 @@
         <v>97</v>
       </c>
       <c r="B26" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C26" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="D26" t="s">
         <v>97</v>
@@ -1786,10 +1801,10 @@
         <v>99</v>
       </c>
       <c r="B27" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C27" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="D27" t="s">
         <v>99</v>
@@ -1805,10 +1820,10 @@
         <v>101</v>
       </c>
       <c r="B28" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C28" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D28" t="s">
         <v>101</v>
@@ -1824,10 +1839,10 @@
         <v>103</v>
       </c>
       <c r="B29" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C29" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="D29" t="s">
         <v>103</v>
@@ -1843,10 +1858,10 @@
         <v>105</v>
       </c>
       <c r="B30" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C30" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="D30" t="s">
         <v>105</v>
@@ -1854,63 +1869,63 @@
       <c r="E30" t="s">
         <v>106</v>
       </c>
-      <c r="F30" t="s">
-        <v>358</v>
-      </c>
-      <c r="G30" t="s">
-        <v>107</v>
-      </c>
-      <c r="H30" t="s">
-        <v>108</v>
-      </c>
+      <c r="G30"/>
+      <c r="H30"/>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B31" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C31" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="D31" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G31"/>
       <c r="H31"/>
     </row>
     <row r="32">
       <c r="A32" t="s">
+        <v>109</v>
+      </c>
+      <c r="B32" t="s">
+        <v>244</v>
+      </c>
+      <c r="C32" t="s">
+        <v>283</v>
+      </c>
+      <c r="D32" t="s">
+        <v>109</v>
+      </c>
+      <c r="E32" t="s">
+        <v>110</v>
+      </c>
+      <c r="F32" t="s">
+        <v>365</v>
+      </c>
+      <c r="G32" t="s">
         <v>111</v>
       </c>
-      <c r="B32" t="s">
-        <v>237</v>
-      </c>
-      <c r="C32" t="s">
-        <v>278</v>
-      </c>
-      <c r="D32" t="s">
-        <v>111</v>
-      </c>
-      <c r="E32" t="s">
+      <c r="H32" t="s">
         <v>112</v>
       </c>
-      <c r="G32"/>
-      <c r="H32"/>
     </row>
     <row r="33">
       <c r="A33" t="s">
         <v>113</v>
       </c>
       <c r="B33" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C33" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="D33" t="s">
         <v>113</v>
@@ -1926,10 +1941,10 @@
         <v>115</v>
       </c>
       <c r="B34" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C34" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="D34" t="s">
         <v>115</v>
@@ -1945,10 +1960,10 @@
         <v>117</v>
       </c>
       <c r="B35" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C35" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="D35" t="s">
         <v>117</v>
@@ -1964,941 +1979,938 @@
         <v>119</v>
       </c>
       <c r="B36" t="s">
-        <v>237</v>
-      </c>
-      <c r="C36" t="s">
-        <v>282</v>
+        <v>9</v>
       </c>
       <c r="D36" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E36" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G36"/>
       <c r="H36"/>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B37" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C37" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D37" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E37" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G37"/>
       <c r="H37"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B38" t="s">
         <v>244</v>
       </c>
       <c r="C38" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D38" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E38" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G38"/>
       <c r="H38"/>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B39" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C39" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D39" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E39" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G39"/>
       <c r="H39"/>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B40" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C40" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D40" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E40" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G40"/>
       <c r="H40"/>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B41" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="C41" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D41" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E41" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G41"/>
       <c r="H41"/>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B42" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C42" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D42" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E42" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G42"/>
       <c r="H42"/>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B43" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C43" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="D43" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E43" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G43"/>
       <c r="H43"/>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B44" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C44" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D44" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E44" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G44"/>
       <c r="H44"/>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B45" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C45" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D45" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E45" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G45"/>
       <c r="H45"/>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B46" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C46" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D46" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E46" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G46"/>
       <c r="H46"/>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B47" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C47" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D47" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E47" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G47"/>
       <c r="H47"/>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B48" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C48" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D48" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E48" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G48"/>
       <c r="H48"/>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B49" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C49" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D49" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E49" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G49"/>
       <c r="H49"/>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B50" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C50" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="D50" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E50" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G50"/>
       <c r="H50"/>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B51" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C51" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="D51" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E51" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G51"/>
       <c r="H51"/>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B52" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C52" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="D52" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E52" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G52"/>
       <c r="H52"/>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B53" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C53" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="D53" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E53" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G53"/>
       <c r="H53"/>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B54" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C54" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D54" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E54" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G54"/>
       <c r="H54"/>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B55" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C55" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="D55" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E55" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G55"/>
       <c r="H55"/>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B56" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C56" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D56" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E56" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G56"/>
       <c r="H56"/>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B57" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C57" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D57" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E57" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G57"/>
       <c r="H57"/>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B58" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C58" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D58" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E58" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G58"/>
       <c r="H58"/>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B59" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C59" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="D59" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E59" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G59"/>
       <c r="H59"/>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B60" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C60" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D60" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E60" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G60"/>
       <c r="H60"/>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B61" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C61" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D61" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E61" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G61"/>
       <c r="H61"/>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B62" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C62" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D62" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E62" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G62"/>
       <c r="H62"/>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B63" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C63" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D63" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E63" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G63"/>
       <c r="H63"/>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B64" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C64" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D64" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E64" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G64"/>
       <c r="H64"/>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B65" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C65" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="D65" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E65" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G65"/>
       <c r="H65"/>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B66" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C66" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D66" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E66" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G66"/>
       <c r="H66"/>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B67" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C67" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D67" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E67" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G67"/>
       <c r="H67"/>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B68" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C68" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="D68" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E68" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G68"/>
       <c r="H68"/>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B69" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C69" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D69" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E69" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G69"/>
       <c r="H69"/>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B70" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C70" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="D70" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E70" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G70"/>
       <c r="H70"/>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B71" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C71" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="D71" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E71" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G71"/>
       <c r="H71"/>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B72" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C72" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="D72" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E72" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G72"/>
       <c r="H72"/>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B73" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="C73" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D73" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E73" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G73"/>
       <c r="H73"/>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B74" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C74" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="D74" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E74" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G74"/>
       <c r="H74"/>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B75" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C75" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D75" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E75" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G75"/>
       <c r="H75"/>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B76" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C76" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="D76" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E76" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G76"/>
       <c r="H76"/>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B77" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C77" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D77" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E77" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G77"/>
       <c r="H77"/>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B78" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C78" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D78" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E78" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G78"/>
       <c r="H78"/>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B79" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C79" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="D79" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E79" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G79"/>
       <c r="H79"/>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B80" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C80" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="D80" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E80" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G80"/>
       <c r="H80"/>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B81" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C81" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D81" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E81" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G81"/>
       <c r="H81"/>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B82" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="C82" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D82" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E82" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G82"/>
       <c r="H82"/>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B83" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C83" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="D83" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E83" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G83"/>
       <c r="H83"/>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B84" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C84" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D84" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E84" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G84"/>
       <c r="H84"/>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B85" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C85" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D85" t="s">
         <v>218</v>
@@ -2914,10 +2926,10 @@
         <v>220</v>
       </c>
       <c r="B86" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C86" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="D86" t="s">
         <v>220</v>
@@ -2933,10 +2945,10 @@
         <v>222</v>
       </c>
       <c r="B87" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C87" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="D87" t="s">
         <v>222</v>
@@ -2952,67 +2964,67 @@
         <v>224</v>
       </c>
       <c r="B88" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="C88" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="D88" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E88" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G88"/>
       <c r="H88"/>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B89" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C89" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D89" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E89" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G89"/>
       <c r="H89"/>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B90" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C90" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="D90" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E90" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G90"/>
       <c r="H90"/>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B91" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C91" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="D91" t="s">
         <v>231</v>
@@ -3028,10 +3040,10 @@
         <v>233</v>
       </c>
       <c r="B92" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C92" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="D92" t="s">
         <v>233</v>
@@ -3041,6 +3053,63 @@
       </c>
       <c r="G92"/>
       <c r="H92"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>235</v>
+      </c>
+      <c r="B93" t="s">
+        <v>254</v>
+      </c>
+      <c r="C93" t="s">
+        <v>343</v>
+      </c>
+      <c r="D93" t="s">
+        <v>235</v>
+      </c>
+      <c r="E93" t="s">
+        <v>236</v>
+      </c>
+      <c r="G93"/>
+      <c r="H93"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>237</v>
+      </c>
+      <c r="B94" t="s">
+        <v>248</v>
+      </c>
+      <c r="C94" t="s">
+        <v>344</v>
+      </c>
+      <c r="D94" t="s">
+        <v>238</v>
+      </c>
+      <c r="E94" t="s">
+        <v>239</v>
+      </c>
+      <c r="G94"/>
+      <c r="H94"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>240</v>
+      </c>
+      <c r="B95" t="s">
+        <v>255</v>
+      </c>
+      <c r="C95" t="s">
+        <v>345</v>
+      </c>
+      <c r="D95" t="s">
+        <v>240</v>
+      </c>
+      <c r="E95" t="s">
+        <v>241</v>
+      </c>
+      <c r="G95"/>
+      <c r="H95"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:H2"/>
